--- a/docs/design/07_テスト設計書_HackerLake.xlsx
+++ b/docs/design/07_テスト設計書_HackerLake.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phrx4\hackerlake\docs\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C65E1173-DD24-44D8-9753-ACEF30AC2A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E24EEF9F-7DEF-49AD-9A20-0C5FAED5B308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{04A21766-95FF-45AD-8757-A6FD26513535}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{A8C99A40-50AE-4C13-BD30-ADE99714C8F5}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,16 @@
     <sheet name="テストケース" sheetId="3" r:id="rId3"/>
     <sheet name="受入基準" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">テストケース!$A$3:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">テスト方針!$A$3:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">受入基準!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">表紙!$A$3:$H$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">テストケース!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">テスト方針!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">受入基準!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">表紙!$1:$3</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -433,7 +443,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -460,15 +470,21 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -484,6 +500,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF006080"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FAFC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -517,7 +539,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -525,12 +547,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -846,18 +871,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB33725-A962-4B0C-8FE1-53166B133A75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE83E0AB-3C0E-491B-924B-057E89944447}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -869,7 +898,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -895,7 +924,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -913,33 +942,33 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>46186</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -966,27 +995,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H6" xr:uid="{AE83E0AB-3C0E-491B-924B-057E89944447}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2369571D-A0A9-43B6-96B9-955C28EB45D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E68054EC-BA0B-414A-8C1B-B97155A14EDE}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -998,7 +1033,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -1024,7 +1059,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -1048,31 +1083,31 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
@@ -1096,52 +1131,58 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H7" xr:uid="{E68054EC-BA0B-414A-8C1B-B97155A14EDE}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AB47B48-C260-4DCA-A56B-1DDBDBD0FA1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91161C24-E6D6-4DAE-BA6B-199E4CF98009}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
@@ -1153,7 +1194,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
@@ -1179,7 +1220,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>65</v>
       </c>
@@ -1205,33 +1246,33 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>76</v>
       </c>
@@ -1257,33 +1298,33 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>89</v>
       </c>
@@ -1309,33 +1350,33 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>100</v>
       </c>
@@ -1362,27 +1403,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H10" xr:uid="{91161C24-E6D6-4DAE-BA6B-199E4CF98009}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0876A09B-8C6B-4E77-9D1B-616425FA34DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{414D864A-BC8E-4659-8B2D-4174996F80E6}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
@@ -1394,7 +1441,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -1420,7 +1467,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>112</v>
       </c>
@@ -1444,31 +1491,31 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>122</v>
       </c>
@@ -1492,31 +1539,31 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>129</v>
       </c>
@@ -1541,10 +1588,12 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H8" xr:uid="{414D864A-BC8E-4659-8B2D-4174996F80E6}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>